--- a/data/external/Info tags_setpoints _limites de operação.xlsx
+++ b/data/external/Info tags_setpoints _limites de operação.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/admin/Documents/GitHub/theasis/data/external/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BA6A0D2-9DD0-994E-AE76-14C9DE2B81E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9705EB5E-F64D-F840-9EFF-BB456F7FFDF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28800" yWindow="-820" windowWidth="38400" windowHeight="19660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
